--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>92852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,32 +1301,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1334,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R7" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B8" t="n">
-        <v>92847</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,26 +1402,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R8" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B7" t="n">
-        <v>92855</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,26 +1301,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1328,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R7" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>92862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,32 +1408,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R8" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92844</v>
+        <v>92851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,32 +1301,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1334,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R7" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B8" t="n">
-        <v>92862</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,26 +1402,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R8" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,26 +1301,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1328,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R7" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,32 +1408,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R8" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92853</v>
+        <v>92839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,32 +1301,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1334,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R7" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,26 +1402,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R8" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B7" t="n">
-        <v>92858</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,26 +1301,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1328,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R7" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>92858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,32 +1408,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R8" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91049</v>
+        <v>91052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>129056179</v>
       </c>
       <c r="B8" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91052</v>
+        <v>91054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92843</v>
+        <v>92845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,32 +1301,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1334,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R7" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B8" t="n">
-        <v>92861</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,26 +1402,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R8" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91054</v>
+        <v>91058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92845</v>
+        <v>92849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,26 +1301,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1328,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R7" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>92867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,32 +1408,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R8" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91058</v>
+        <v>91059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92849</v>
+        <v>92850</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129056183</v>
+        <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>92868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,32 +1301,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1334,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687684</v>
+        <v>687691</v>
       </c>
       <c r="R7" t="n">
-        <v>6614777</v>
+        <v>6614811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129056179</v>
+        <v>129056183</v>
       </c>
       <c r="B8" t="n">
-        <v>92867</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,26 +1402,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687691</v>
+        <v>687684</v>
       </c>
       <c r="R8" t="n">
-        <v>6614811</v>
+        <v>6614777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42612-2025 artfynd.xlsx
+++ b/artfynd/A 42612-2025 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>129056171</v>
       </c>
       <c r="B5" t="n">
-        <v>91059</v>
+        <v>91062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>129056181</v>
       </c>
       <c r="B6" t="n">
-        <v>92850</v>
+        <v>92853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129056179</v>
       </c>
       <c r="B7" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>129056182</v>
       </c>
       <c r="B9" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
